--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J54-Profession-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J54-Profession-ROR.xlsx
@@ -12,12 +12,13 @@
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
     <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="146">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250523120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,6 +441,21 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Infirmier expert en plaies et cicatrisation</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>Sexologue</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R356-ProfessionRessource/FHIR/TRE-R356-ProfessionRessource</t>
   </si>
 </sst>
 </file>
@@ -1311,4 +1327,58 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>